--- a/samples/oracle_liquidity.xlsx
+++ b/samples/oracle_liquidity.xlsx
@@ -4764,7 +4764,7 @@
                 <ns1:cs typeface="Arial"/>
               </ns1:rPr>
               <ns1:t>Principal at Aug 31, 2026 (USD billions)
-FY2027 remainder; thereafter = FY2032 onward</ns1:t>
+FY2027 remainder. Scale ends at $12B; the hatched Thereafter bar (FY2032-FY2066 combined, $90.3B) runs past it</ns1:t>
             </ns1:r>
           </ns1:p>
         </ns0:rich>
@@ -4800,6 +4800,44 @@
             </ns1:solidFill>
           </ns0:spPr>
           <ns0:invertIfNegative val="0"/>
+          <ns0:dPt>
+            <ns0:idx val="5"/>
+            <ns0:invertIfNegative val="0"/>
+            <ns0:bubble3D val="0"/>
+            <ns0:spPr>
+              <ns1:pattFill prst="wdUpDiag">
+                <ns1:fgClr>
+                  <ns1:srgbClr val="D95926"/>
+                </ns1:fgClr>
+                <ns1:bgClr>
+                  <ns1:srgbClr val="F6D2C2"/>
+                </ns1:bgClr>
+              </ns1:pattFill>
+            </ns0:spPr>
+          </ns0:dPt>
+          <ns0:dLbls>
+            <ns0:numFmt formatCode="&quot;$&quot;#,##0.0,,,&quot;B&quot;" sourceLinked="0"/>
+            <ns0:txPr>
+              <ns1:bodyPr/>
+              <ns1:lstStyle/>
+              <ns1:p>
+                <ns1:pPr>
+                  <ns1:defRPr sz="750" b="1">
+                    <ns1:latin typeface="Arial"/>
+                    <ns1:ea typeface="Arial"/>
+                    <ns1:cs typeface="Arial"/>
+                  </ns1:defRPr>
+                </ns1:pPr>
+              </ns1:p>
+            </ns0:txPr>
+            <ns0:dLblPos val="inEnd"/>
+            <ns0:showLegendKey val="0"/>
+            <ns0:showVal val="1"/>
+            <ns0:showCatName val="0"/>
+            <ns0:showSerName val="0"/>
+            <ns0:showPercent val="0"/>
+            <ns0:showBubbleSize val="0"/>
+          </ns0:dLbls>
           <ns0:cat>
             <ns0:strRef>
               <ns0:f>'Payment dates'!$A$49:$A$54</ns0:f>
@@ -4897,6 +4935,8 @@
         <ns0:axId val="48672768"/>
         <ns0:scaling>
           <ns0:orientation val="minMax"/>
+          <ns0:max val="12000000000"/>
+          <ns0:min val="0"/>
         </ns0:scaling>
         <ns0:delete val="0"/>
         <ns0:axPos val="l"/>
@@ -4942,6 +4982,7 @@
         </ns0:txPr>
         <ns0:crossAx val="48650112"/>
         <ns0:crossBetween val="between"/>
+        <ns0:majorUnit val="2000000000"/>
       </ns0:valAx>
     </ns0:plotArea>
     <ns0:plotVisOnly val="1"/>
@@ -6161,7 +6202,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="356" t="str">
-        <x:v>Balance sheet 2026-08-31. TTM 2025-09-01 to 2026-08-31. USD millions unless x or %.</x:v>
+        <x:v>Balance sheet 2026-08-31. TTM 2025-09-01 to 2026-08-31. USD millions, except ratios (x) and percentages (%).</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -6409,7 +6450,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="315" t="str">
-        <x:v>USD millions unless x or %. Fiscal year and later TTM both span twelve months and overlap.</x:v>
+        <x:v>USD millions, except ratios (x) and percentages (%). Fiscal year and later TTM both span twelve months and overlap.</x:v>
       </x:c>
       <x:c r="B3" s="331"/>
       <x:c r="C3" s="331"/>
@@ -12132,7 +12173,7 @@
         <x:v>Key</x:v>
       </x:c>
       <x:c r="B1" s="381" t="str">
-        <x:v>USD millions unless x</x:v>
+        <x:v>USD millions, except ratios (x)</x:v>
       </x:c>
       <x:c r="C1" s="381" t="str">
         <x:v>Reported input</x:v>
@@ -15568,7 +15609,7 @@
       </x:c>
       <x:c r="O77" s="480" t="str"/>
       <x:c r="P77" s="387" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="Q77" s="387" t="str">
         <x:v>61a353e222f961e516bb3e8eed024a5245cfadbf30e3cc16a4a520129f1bdf63</x:v>
@@ -15622,7 +15663,7 @@
       </x:c>
       <x:c r="O78" s="480" t="str"/>
       <x:c r="P78" s="387" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="Q78" s="387" t="str">
         <x:v>61a353e222f961e516bb3e8eed024a5245cfadbf30e3cc16a4a520129f1bdf63</x:v>
@@ -15676,7 +15717,7 @@
       </x:c>
       <x:c r="O79" s="480" t="str"/>
       <x:c r="P79" s="387" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="Q79" s="387" t="str">
         <x:v>61a353e222f961e516bb3e8eed024a5245cfadbf30e3cc16a4a520129f1bdf63</x:v>
@@ -15730,7 +15771,7 @@
       </x:c>
       <x:c r="O80" s="480" t="str"/>
       <x:c r="P80" s="387" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="Q80" s="387" t="str">
         <x:v>051dd4893fa497f36d99c8a355cbc90107f56e1a628c78e38c76e7dca0d4a6fd</x:v>
@@ -15784,7 +15825,7 @@
       </x:c>
       <x:c r="O81" s="480" t="str"/>
       <x:c r="P81" s="387" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="Q81" s="387" t="str">
         <x:v>051dd4893fa497f36d99c8a355cbc90107f56e1a628c78e38c76e7dca0d4a6fd</x:v>
@@ -15838,7 +15879,7 @@
       </x:c>
       <x:c r="O82" s="480" t="str"/>
       <x:c r="P82" s="387" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="Q82" s="387" t="str">
         <x:v>051dd4893fa497f36d99c8a355cbc90107f56e1a628c78e38c76e7dca0d4a6fd</x:v>
@@ -15892,7 +15933,7 @@
       </x:c>
       <x:c r="O83" s="480" t="str"/>
       <x:c r="P83" s="387" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="Q83" s="387" t="str">
         <x:v>051dd4893fa497f36d99c8a355cbc90107f56e1a628c78e38c76e7dca0d4a6fd</x:v>
@@ -15946,7 +15987,7 @@
       </x:c>
       <x:c r="O84" s="480" t="str"/>
       <x:c r="P84" s="387" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="Q84" s="387" t="str">
         <x:v>051dd4893fa497f36d99c8a355cbc90107f56e1a628c78e38c76e7dca0d4a6fd</x:v>
@@ -16000,7 +16041,7 @@
       </x:c>
       <x:c r="O85" s="480" t="str"/>
       <x:c r="P85" s="387" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="Q85" s="387" t="str">
         <x:v>051dd4893fa497f36d99c8a355cbc90107f56e1a628c78e38c76e7dca0d4a6fd</x:v>
@@ -16256,7 +16297,7 @@
         <x:v>Key</x:v>
       </x:c>
       <x:c r="B102" s="332" t="str">
-        <x:v>USD millions unless x</x:v>
+        <x:v>USD millions, except ratios (x)</x:v>
       </x:c>
       <x:c r="C102" s="332" t="str">
         <x:v>Reported input</x:v>
@@ -16344,7 +16385,7 @@
       </x:c>
       <x:c r="O103" s="366" t="str"/>
       <x:c r="P103" s="335" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="Q103" s="366" t="str"/>
       <x:c r="R103" s="319" t="str">
@@ -16388,7 +16429,7 @@
       </x:c>
       <x:c r="O104" s="366" t="str"/>
       <x:c r="P104" s="335" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="Q104" s="366" t="str"/>
       <x:c r="R104" s="319" t="str">
@@ -16438,7 +16479,7 @@
       </x:c>
       <x:c r="O105" s="366" t="str"/>
       <x:c r="P105" s="335" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="Q105" s="335" t="str">
         <x:v>051dd4893fa497f36d99c8a355cbc90107f56e1a628c78e38c76e7dca0d4a6fd</x:v>
@@ -16490,7 +16531,7 @@
       </x:c>
       <x:c r="O106" s="366" t="str"/>
       <x:c r="P106" s="335" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="Q106" s="335" t="str">
         <x:v>051dd4893fa497f36d99c8a355cbc90107f56e1a628c78e38c76e7dca0d4a6fd</x:v>
@@ -16542,7 +16583,7 @@
       </x:c>
       <x:c r="O107" s="366" t="str"/>
       <x:c r="P107" s="335" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="Q107" s="335" t="str">
         <x:v>051dd4893fa497f36d99c8a355cbc90107f56e1a628c78e38c76e7dca0d4a6fd</x:v>
@@ -16594,7 +16635,7 @@
       </x:c>
       <x:c r="O108" s="366" t="str"/>
       <x:c r="P108" s="335" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="Q108" s="335" t="str">
         <x:v>051dd4893fa497f36d99c8a355cbc90107f56e1a628c78e38c76e7dca0d4a6fd</x:v>
@@ -16646,7 +16687,7 @@
       </x:c>
       <x:c r="O109" s="366" t="str"/>
       <x:c r="P109" s="335" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="Q109" s="335" t="str">
         <x:v>051dd4893fa497f36d99c8a355cbc90107f56e1a628c78e38c76e7dca0d4a6fd</x:v>
@@ -16698,7 +16739,7 @@
       </x:c>
       <x:c r="O110" s="366" t="str"/>
       <x:c r="P110" s="335" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="Q110" s="335" t="str">
         <x:v>051dd4893fa497f36d99c8a355cbc90107f56e1a628c78e38c76e7dca0d4a6fd</x:v>
@@ -16752,7 +16793,7 @@
         <x:v>Amount reported in rounded billions. Future commitment, not a recognized lease liability. Expected to commence Q2 fiscal 2027–fiscal 2029, with 15–19 year terms. Annual payment timing is Unavailable.</x:v>
       </x:c>
       <x:c r="P111" s="491" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="Q111" s="491" t="str">
         <x:v>051dd4893fa497f36d99c8a355cbc90107f56e1a628c78e38c76e7dca0d4a6fd</x:v>
@@ -16766,7 +16807,7 @@
         <x:v>Key</x:v>
       </x:c>
       <x:c r="B114" s="332" t="str">
-        <x:v>USD millions unless x</x:v>
+        <x:v>USD millions, except ratios (x)</x:v>
       </x:c>
       <x:c r="C114" s="332" t="str">
         <x:v>Reported input</x:v>
@@ -16856,7 +16897,7 @@
         <x:v>USD instant at the balance-sheet date, from the latest original 10-K or 10-Q itself</x:v>
       </x:c>
       <x:c r="P115" s="335" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="Q115" s="366"/>
       <x:c r="R115" s="319" t="str">
@@ -16902,7 +16943,7 @@
         <x:v>USD instant at the balance-sheet date, from the latest original 10-K or 10-Q itself</x:v>
       </x:c>
       <x:c r="P116" s="335" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="Q116" s="366"/>
       <x:c r="R116" s="319" t="str">
@@ -16948,7 +16989,7 @@
         <x:v>USD instant at the balance-sheet date, from the latest original 10-K or 10-Q itself</x:v>
       </x:c>
       <x:c r="P117" s="335" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="Q117" s="366"/>
       <x:c r="R117" s="319" t="str">
@@ -16994,7 +17035,7 @@
         <x:v>USD instant at the balance-sheet date, from the latest original 10-K or 10-Q itself</x:v>
       </x:c>
       <x:c r="P118" s="335" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="Q118" s="366"/>
       <x:c r="R118" s="319" t="str">
@@ -17040,7 +17081,7 @@
         <x:v>USD instant at the balance-sheet date, from the latest original 10-K or 10-Q itself</x:v>
       </x:c>
       <x:c r="P119" s="335" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="Q119" s="366"/>
       <x:c r="R119" s="319" t="str">
@@ -17094,7 +17135,7 @@
         <x:v>Exact tag, USD duration, exact start and end dates, no dimensions</x:v>
       </x:c>
       <x:c r="P120" s="335" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="Q120" s="366"/>
       <x:c r="R120" s="319" t="str">
@@ -17148,7 +17189,7 @@
         <x:v>Exact tag, USD duration, exact start and end dates, no dimensions</x:v>
       </x:c>
       <x:c r="P121" s="335" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="Q121" s="366"/>
       <x:c r="R121" s="319" t="str">
@@ -17202,7 +17243,7 @@
         <x:v>Exact tag, USD duration, exact start and end dates, no dimensions</x:v>
       </x:c>
       <x:c r="P122" s="335" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="Q122" s="366"/>
       <x:c r="R122" s="319" t="str">
@@ -17256,7 +17297,7 @@
         <x:v>Exact tag, USD duration, exact start and end dates, no dimensions</x:v>
       </x:c>
       <x:c r="P123" s="335" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="Q123" s="366"/>
       <x:c r="R123" s="319" t="str">
@@ -17310,7 +17351,7 @@
         <x:v>Exact tag, USD duration, exact start and end dates, no dimensions</x:v>
       </x:c>
       <x:c r="P124" s="335" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="Q124" s="366"/>
       <x:c r="R124" s="319" t="str">
@@ -17364,7 +17405,7 @@
         <x:v>Exact tag, USD duration, exact start and end dates, no dimensions</x:v>
       </x:c>
       <x:c r="P125" s="491" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="Q125" s="367"/>
       <x:c r="R125" s="321" t="str">
@@ -17376,7 +17417,7 @@
         <x:v>Key</x:v>
       </x:c>
       <x:c r="B128" s="332" t="str">
-        <x:v>USD millions unless x</x:v>
+        <x:v>USD millions, except ratios (x)</x:v>
       </x:c>
       <x:c r="C128" s="332" t="str">
         <x:v>Reported input</x:v>
@@ -17472,7 +17513,7 @@
         <x:v>USD instant at the balance-sheet date, from the latest original 10-K or 10-Q itself</x:v>
       </x:c>
       <x:c r="P129" s="335" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="Q129" s="335" t="str">
         <x:v>61a353e222f961e516bb3e8eed024a5245cfadbf30e3cc16a4a520129f1bdf63</x:v>
@@ -17526,7 +17567,7 @@
         <x:v>USD instant at the balance-sheet date, from the latest original 10-K or 10-Q itself</x:v>
       </x:c>
       <x:c r="P130" s="335" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="Q130" s="335" t="str">
         <x:v>61a353e222f961e516bb3e8eed024a5245cfadbf30e3cc16a4a520129f1bdf63</x:v>
@@ -17580,7 +17621,7 @@
         <x:v>USD instant at the balance-sheet date, from the latest original 10-K or 10-Q itself</x:v>
       </x:c>
       <x:c r="P131" s="335" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="Q131" s="335" t="str">
         <x:v>61a353e222f961e516bb3e8eed024a5245cfadbf30e3cc16a4a520129f1bdf63</x:v>
@@ -17634,7 +17675,7 @@
         <x:v>USD instant at the balance-sheet date, from the latest original 10-K or 10-Q itself</x:v>
       </x:c>
       <x:c r="P132" s="335" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="Q132" s="335" t="str">
         <x:v>61a353e222f961e516bb3e8eed024a5245cfadbf30e3cc16a4a520129f1bdf63</x:v>
@@ -17688,7 +17729,7 @@
         <x:v>USD instant at the balance-sheet date, from the latest original 10-K or 10-Q itself</x:v>
       </x:c>
       <x:c r="P133" s="335" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="Q133" s="335" t="str">
         <x:v>61a353e222f961e516bb3e8eed024a5245cfadbf30e3cc16a4a520129f1bdf63</x:v>
@@ -17744,7 +17785,7 @@
         <x:v>Exact tag, USD duration, exact start and end dates, no dimensions</x:v>
       </x:c>
       <x:c r="P134" s="335" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="Q134" s="366" t="str"/>
       <x:c r="R134" s="319" t="str">
@@ -17798,7 +17839,7 @@
         <x:v>Exact tag, USD duration, exact start and end dates, no dimensions</x:v>
       </x:c>
       <x:c r="P135" s="491" t="str">
-        <x:v>[]</x:v>
+        <x:v>None (consolidated total)</x:v>
       </x:c>
       <x:c r="Q135" s="367" t="str"/>
       <x:c r="R135" s="321" t="str">

--- a/samples/oracle_liquidity.xlsx
+++ b/samples/oracle_liquidity.xlsx
@@ -10373,6 +10373,12 @@
       <x:c r="D48" s="470" t="str">
         <x:v>Through</x:v>
       </x:c>
+      <x:c r="E48" s="469" t="str">
+        <x:v>FY2032 onward, by decade</x:v>
+      </x:c>
+      <x:c r="F48" s="470" t="str">
+        <x:v>Principal (USD millions)</x:v>
+      </x:c>
     </x:row>
     <x:row r="49" ht="18" customHeight="1">
       <x:c r="A49" s="378" t="str">
@@ -10388,6 +10394,13 @@
       <x:c r="D49" s="471" t="d">
         <x:v>2027-05-31T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="E49" s="378" t="str">
+        <x:v>FY2032–36</x:v>
+      </x:c>
+      <x:c r="F49" s="472" t="n">
+        <x:f>SUMIFS($E$95:$E$152,$B$95:$B$152,"&gt;="&amp;DATE(2031,6,1),$B$95:$B$152,"&lt;="&amp;DATE(2036,5,31),$F$95:$F$152,"&lt;&gt;Term loan")</x:f>
+        <x:v>26500000000</x:v>
+      </x:c>
     </x:row>
     <x:row r="50" ht="18" customHeight="1">
       <x:c r="A50" s="378" t="str">
@@ -10403,6 +10416,13 @@
       <x:c r="D50" s="471" t="d">
         <x:v>2028-05-31T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="E50" s="378" t="str">
+        <x:v>FY2037–46</x:v>
+      </x:c>
+      <x:c r="F50" s="472" t="n">
+        <x:f>SUMIFS($E$95:$E$152,$B$95:$B$152,"&gt;="&amp;DATE(2036,6,1),$B$95:$B$152,"&lt;="&amp;DATE(2046,5,31),$F$95:$F$152,"&lt;&gt;Term loan")</x:f>
+        <x:v>20750000000</x:v>
+      </x:c>
     </x:row>
     <x:row r="51" ht="18" customHeight="1">
       <x:c r="A51" s="378" t="str">
@@ -10418,6 +10438,13 @@
       <x:c r="D51" s="471" t="d">
         <x:v>2029-05-31T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="E51" s="378" t="str">
+        <x:v>FY2047–56</x:v>
+      </x:c>
+      <x:c r="F51" s="472" t="n">
+        <x:f>SUMIFS($E$95:$E$152,$B$95:$B$152,"&gt;="&amp;DATE(2046,6,1),$B$95:$B$152,"&lt;="&amp;DATE(2056,5,31),$F$95:$F$152,"&lt;&gt;Term loan")</x:f>
+        <x:v>31000000000</x:v>
+      </x:c>
     </x:row>
     <x:row r="52" ht="18" customHeight="1">
       <x:c r="A52" s="378" t="str">
@@ -10433,6 +10460,13 @@
       <x:c r="D52" s="471" t="d">
         <x:v>2030-05-31T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="E52" s="378" t="str">
+        <x:v>FY2057–66</x:v>
+      </x:c>
+      <x:c r="F52" s="472" t="n">
+        <x:f>SUMIFS($E$95:$E$152,$B$95:$B$152,"&gt;="&amp;DATE(2056,6,1),$B$95:$B$152,"&lt;="&amp;DATE(2066,5,31),$F$95:$F$152,"&lt;&gt;Term loan")</x:f>
+        <x:v>12000000000</x:v>
+      </x:c>
     </x:row>
     <x:row r="53" ht="18" customHeight="1">
       <x:c r="A53" s="378" t="str">
@@ -10448,6 +10482,13 @@
       <x:c r="D53" s="471" t="d">
         <x:v>2031-05-31T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="E53" s="473" t="str">
+        <x:v>Sum of decades</x:v>
+      </x:c>
+      <x:c r="F53" s="474" t="n">
+        <x:f>SUM(F49:F52)</x:f>
+        <x:v>90250000000</x:v>
+      </x:c>
     </x:row>
     <x:row r="54" ht="18" customHeight="1">
       <x:c r="A54" s="378" t="str">
@@ -10462,6 +10503,13 @@
       </x:c>
       <x:c r="D54" s="411" t="str">
         <x:v>Final maturity</x:v>
+      </x:c>
+      <x:c r="E54" s="378" t="str">
+        <x:v>Less Thereafter (C54); should be 0</x:v>
+      </x:c>
+      <x:c r="F54" s="472" t="n">
+        <x:f>F53-C54</x:f>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="18" customHeight="1">

--- a/samples/oracle_liquidity.xlsx
+++ b/samples/oracle_liquidity.xlsx
@@ -17699,6 +17699,674 @@
 </ns0:chartSpace>
 </file>
 
+<file path=xl/drawings/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1100" b="1">
+                <a:latin typeface="Arial"/>
+              </a:rPr>
+              <a:t>Fiscal-year-end cash and baseline borrowing (USD millions)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Annual history'!$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Cash and equivalents</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="3987E5"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Annual history'!$B$5:$F$5</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>FY2022</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>FY2023</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>FY2024</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>FY2025</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>FY2026</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Annual history'!$B$6:$F$6</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0,,;(#,##0,,)</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>21383000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9765000000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10454000000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10786000000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>31289000000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Annual history'!$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Baseline borrowing</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="D95926"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Annual history'!$B$5:$F$5</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>FY2022</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>FY2023</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>FY2024</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>FY2025</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>FY2026</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Annual history'!$B$7:$F$7</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0,,;(#,##0,,)</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>75859000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>90481000000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>86869000000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>92568000000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>129541000000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="80"/>
+        <c:axId val="5001"/>
+        <c:axId val="5002"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="5001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0">
+                <a:latin typeface="Arial"/>
+                <a:cs typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="5002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="5002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:srgbClr val="D9D9D9"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" vert="horz"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000">
+                    <a:latin typeface="Arial"/>
+                  </a:rPr>
+                  <a:t>USD millions</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="#,##0,,;(#,##0,,)" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0">
+                <a:latin typeface="Arial"/>
+                <a:cs typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="5001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1000" b="0">
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1000" b="0">
+          <a:latin typeface="Arial"/>
+          <a:cs typeface="Arial"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1100" b="1">
+                <a:latin typeface="Arial"/>
+              </a:rPr>
+              <a:t>Annual operating cash flow, capital spending (a use, below zero) and FCF (USD millions)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Annual history'!$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Operating cash flow</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="3987E5"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Annual history'!$B$5:$F$5</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>FY2022</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>FY2023</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>FY2024</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>FY2025</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>FY2026</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Annual history'!$B$8:$F$8</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0,,;(#,##0,,)</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>9539000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17165000000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18673000000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20821000000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>31977000000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Annual history'!$A$61</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Capital spending (a use of cash)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="7F838C"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Annual history'!$B$5:$F$5</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>FY2022</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>FY2023</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>FY2024</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>FY2025</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>FY2026</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Annual history'!$B$61:$F$61</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0,,;(#,##0,,)</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-4511000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-8695000000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-6866000000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-21215000000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-55663000000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Annual history'!$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Free cash flow</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="47627F"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Annual history'!$B$5:$F$5</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>FY2022</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>FY2023</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>FY2024</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>FY2025</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>FY2026</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Annual history'!$B$10:$F$10</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0,,;(#,##0,,)</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>5028000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8470000000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>11807000000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-394000000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-23686000000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="80"/>
+        <c:axId val="5001"/>
+        <c:axId val="5002"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="5001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0">
+                <a:latin typeface="Arial"/>
+                <a:cs typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="5002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="5002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="6350">
+              <a:solidFill>
+                <a:srgbClr val="D9D9D9"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" vert="horz"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000">
+                    <a:latin typeface="Arial"/>
+                  </a:rPr>
+                  <a:t>USD millions</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="#,##0,,;(#,##0,,)" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0">
+                <a:latin typeface="Arial"/>
+                <a:cs typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="5001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1000" b="0">
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1000" b="0">
+          <a:latin typeface="Arial"/>
+          <a:cs typeface="Arial"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+</c:chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:twoCellAnchor>
@@ -17826,6 +18494,71 @@
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf64a64cfcf6447a3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Annual chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="rIdAnnualBalances"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Annual chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="rIdAnnualFlows"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -18610,7 +19343,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
@@ -18921,8 +19654,39 @@
       <x:c r="F22" s="1046"/>
     </x:row>
     <x:row r="23" ht="21" customHeight="1"/>
+    <x:row r="60">
+      <x:c r="A60" s="1046" t="str">
+        <x:v>Chart data: capital spending as a use of cash, the negative of row 9 (missing years stay #N/A, so they leave a gap).</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="1067" t="str">
+        <x:v>Capital spending (a use of cash)</x:v>
+      </x:c>
+      <x:c r="B61" s="2085" t="n">
+        <x:f>IF(ISNUMBER(B9),-B9,NA())</x:f>
+        <x:v>-4511000000</x:v>
+      </x:c>
+      <x:c r="C61" s="2085" t="n">
+        <x:f>IF(ISNUMBER(C9),-C9,NA())</x:f>
+        <x:v>-8695000000</x:v>
+      </x:c>
+      <x:c r="D61" s="2085" t="n">
+        <x:f>IF(ISNUMBER(D9),-D9,NA())</x:f>
+        <x:v>-6866000000</x:v>
+      </x:c>
+      <x:c r="E61" s="2085" t="n">
+        <x:f>IF(ISNUMBER(E9),-E9,NA())</x:f>
+        <x:v>-21215000000</x:v>
+      </x:c>
+      <x:c r="F61" s="2086" t="n">
+        <x:f>IF(ISNUMBER(F9),-F9,NA())</x:f>
+        <x:v>-55663000000</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing r:id="rIdAnnualCharts"/>
 </x:worksheet>
 </file>
 
